--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:21:25+00:00</t>
+    <t>2026-05-13T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1355,38 +1355,42 @@
 </t>
   </si>
   <si>
-    <t>Die Anzahl der weiteren möglichen Einlösungen ist abhängig von der Rezeptart: Kassenrezept: keine weitere Einlösung möglich (fixer Wert 0). Privatrezept: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden. Sustitutionsrezept: keine weitere Einlösung möglich (fixer Wert 0)</t>
+    <t>Gültigkeitszeitraum einer geplante Abgabe (abhängig von Rezeptart): Kassenrezept: ab Erstelldatum 1 Monat, bei Teilabgabe verlängert sich Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess). Privatrezept: ab Erstelldatum max. 365 Tage, die Gültigkeitsdauer kann vom Arzt definiert werden. Substitutionsrezept: Max. Gültigkeitsdauer 12 Monate.</t>
+  </si>
+  <si>
+    <t>Zeitraum in dem die geplante Abgabe eingelöst werden kann.
+Der Gültigkeitszeitraum ist abhängig von der **Rezeptart**: 
+* **Kassenrezept**: ab Erstelldatum einen Monat gültig (vom Ausstellungszeitpunkt bis zum gleichen Tag des Folgemonats 23:59 Uhr); validityPeriod.start kein Datum in der Zukunft; bei einer Teilabgabe verlängert sich die gesamte Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess).
+* **Privatrezept**: ab Erstelldatum maximal 365 Tage gültig, wenn die erste Einlösung innerhalb von 1 Monat ab Erstelldatum erfolgt (sonst Status abgelaufen). validityPeriod.start kein Datum in der Zukunft; Die Gültigkeitsdauer (validityPeriod.end) kann vom Arzt definiert werden.
+* **Substitutionsrezept**: Maximale Gültigkeitsdauer 12 Monate. Das validityPeriod.start darf maximal einen Monat in der Zukunft liegen, gültig bis das validityPeriod.end erreicht ist.</t>
+  </si>
+  <si>
+    <t>It reflects the prescribers' perspective for the validity of the prescription. Dispenses must not be made against the prescription outside of this period. The lower-bound of the Dispensing Window signifies the earliest date that the prescription can be filled for the first time. If an upper-bound is not specified then the Prescription is open-ended or will default to a stale-date based on regulations.</t>
+  </si>
+  <si>
+    <t>Indicates when the Prescription becomes valid, and when it ceases to be a dispensable Prescription.</t>
+  </si>
+  <si>
+    <t>Message/Body/NewRx/MedicationPrescribed/Refills</t>
+  </si>
+  <si>
+    <t>effectiveTime</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.numberOfRepeatsAllowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsignedInt
+</t>
+  </si>
+  <si>
+    <t>Die Anzahl der weiteren möglichen Einlösungen (abhängig von Rezeptart): Kassenrezept: keine weitere Einlösung möglich (fixer Wert 0). Privatrezept: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden. Sustitutionsrezept: keine weitere Einlösung möglich (fixer Wert 0)</t>
   </si>
   <si>
     <t xml:space="preserve">Anzahl der weiteren möglichen Einlösungen:
 * **Kassenrezept**: keine weitere Einlösung möglich (fixer Wert 0)
 * **Privatrezept**: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden
 * **Sustitutionsrezept**: keine weitere Einlösung möglich (fixer Wert 0) </t>
-  </si>
-  <si>
-    <t>It reflects the prescribers' perspective for the validity of the prescription. Dispenses must not be made against the prescription outside of this period. The lower-bound of the Dispensing Window signifies the earliest date that the prescription can be filled for the first time. If an upper-bound is not specified then the Prescription is open-ended or will default to a stale-date based on regulations.</t>
-  </si>
-  <si>
-    <t>Indicates when the Prescription becomes valid, and when it ceases to be a dispensable Prescription.</t>
-  </si>
-  <si>
-    <t>Message/Body/NewRx/MedicationPrescribed/Refills</t>
-  </si>
-  <si>
-    <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.numberOfRepeatsAllowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unsignedInt
-</t>
-  </si>
-  <si>
-    <t>Number of refills authorized</t>
-  </si>
-  <si>
-    <t>An integer indicating the number of times, in addition to the original dispense, (aka refills or repeats) that the patient can receive the prescribed medication. Usage Notes: This integer does not include the original order dispense. This means that if an order indicates dispense 30 tablets plus "3 repeats", then the order can be dispensed a total of 4 times and the patient can receive a total of 120 tablets.  A prescriber may explicitly say that zero refills are permitted after the initial dispense.</t>
   </si>
   <si>
     <t>If displaying "number of authorized fills", add 1 to this number.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:40:49+00:00</t>
+    <t>2026-05-15T11:09:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:09:11+00:00</t>
+    <t>2026-05-22T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T12:28:16+00:00</t>
+    <t>2026-05-27T13:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -819,7 +819,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
 </t>
   </si>
   <si>
@@ -929,7 +929,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
@@ -2068,7 +2068,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="205.50390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="195.8359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:46:49+00:00</t>
+    <t>2026-05-28T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T11:16:16+00:00</t>
+    <t>2026-06-01T11:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:23:56+00:00</t>
+    <t>2026-06-01T11:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:34:34+00:00</t>
+    <t>2026-06-02T13:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T13:07:12+00:00</t>
+    <t>2026-06-09T15:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:23:07+00:00</t>
+    <t>2026-06-10T09:53:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
-Sie enthält das verordnete Arzneimittel und dessen Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation.
-Werden mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer'). Verwendet R5 Backport Extensions.</t>
+    <t>Bildet eine "Geplante Abgabe" eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource mit Kategorie "Geplante Abgabe"):
+Sie enthält die verordnete Medikation und deren Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation. 
+Werden mehrere Medikamente gleichzeitig verordnet und sollen demselben e-Rezept zugeordnet sein, wird für jedes Medikament eine "Geplante Abgabe" mit demselben "e-Med GroupIdentifier" erstellt (bildet 'Rezept-Klammer'). 
+Es werden R5-Backport-Extensions verwendet.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:53:12+00:00</t>
+    <t>2026-06-10T11:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T11:38:54+00:00</t>
+    <t>2026-06-12T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:35:19+00:00</t>
+    <t>2026-06-15T08:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:37:42+00:00</t>
+    <t>2026-06-15T17:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T17:37:50+00:00</t>
+    <t>2026-06-15T21:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T21:20:33+00:00</t>
+    <t>2026-06-16T10:30:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:30:24+00:00</t>
+    <t>2026-06-16T16:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:59:26+00:00</t>
+    <t>2026-06-17T13:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:25:59+00:00</t>
+    <t>2026-06-19T14:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:53:34+00:00</t>
+    <t>2026-06-22T08:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -563,7 +563,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status der geplanten Abgabe. Mögliche Ausprägung: [active | completed | entered-in-error | stopped]. Bedeutung: active: offene, geplante Abgabe | completed: geplante Abgabe abgeschlossen | entered-in-error: nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde | stopped: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)</t>
+    <t>Status der geplanten Abgabe. Mögliche Ausprägung: [active | completed | entered-in-error | stopped]. Bedeutung: active: offene, Geplante Abgabe | completed: Geplante Abgabe abgeschlossen | entered-in-error: nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde | stopped: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -624,7 +624,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>Die geplante Abgabe stellt einen Auftrag zur Durchführung und eine Autorisierung des Verfassers dar; daher ist intent immer "order".</t>
+    <t>Die Geplante Abgabe stellt einen Auftrag zur Durchführung und eine Autorisierung des Verfassers dar; daher ist intent immer "order".</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -751,7 +751,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, ob die geplante Abgabe untersagt ist. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Gibt an, ob die Geplante Abgabe untersagt ist. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>If true indicates that the provider is asking for the medication request not to occur.</t>
@@ -824,7 +824,7 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den die geplante Abgabe ausgestellt werden soll (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
+    <t>Patient, für den die Geplante Abgabe ausgestellt werden soll (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -857,7 +857,7 @@
 </t>
   </si>
   <si>
-    <t>Aufenthalt/Begegnung, während dessen die geplante Abgabe erstellt wurde. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Aufenthalt/Begegnung, während dessen die Geplante Abgabe erstellt wurde. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
@@ -934,7 +934,7 @@
 </t>
   </si>
   <si>
-    <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
+    <t>Der Arzt oder die Ärztin, die die Geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
 (eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
   </si>
   <si>
@@ -1101,7 +1101,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf die (aktuelle) Version des zugrundeliegenden Medikationsplaneintrags, auf dem diese geplante Abgabe basiert.</t>
+    <t>Referenz auf die (aktuelle) Version des zugrundeliegenden Medikationsplaneintrags, auf dem diese Geplante Abgabe basiert.</t>
   </si>
   <si>
     <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
@@ -1118,7 +1118,7 @@
   <si>
     <t>Als groupIdentifier dient die eMED-ID, die auch im e-Rezept mitgeführt wird. 
 Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine 
-geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
+Geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>
@@ -1356,10 +1356,10 @@
 </t>
   </si>
   <si>
-    <t>Gültigkeitszeitraum einer geplante Abgabe (abhängig von Rezeptart): Kassenrezept: ab Erstelldatum 1 Monat, bei Teilabgabe verlängert sich Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess). Privatrezept: ab Erstelldatum max. 365 Tage, die Gültigkeitsdauer kann vom Arzt definiert werden. Substitutionsrezept: Max. Gültigkeitsdauer 12 Monate.</t>
-  </si>
-  <si>
-    <t>Zeitraum in dem die geplante Abgabe eingelöst werden kann.
+    <t>Gültigkeitszeitraum einer Geplante Abgabe (abhängig von Rezeptart): Kassenrezept: ab Erstelldatum 1 Monat, bei Teilabgabe verlängert sich Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess). Privatrezept: ab Erstelldatum max. 365 Tage, die Gültigkeitsdauer kann vom Arzt definiert werden. Substitutionsrezept: Max. Gültigkeitsdauer 12 Monate.</t>
+  </si>
+  <si>
+    <t>Zeitraum in dem die Geplante Abgabe eingelöst werden kann.
 Der Gültigkeitszeitraum ist abhängig von der **Rezeptart**: 
 * **Kassenrezept**: ab Erstelldatum einen Monat gültig (vom Ausstellungszeitpunkt bis zum gleichen Tag des Folgemonats 23:59 Uhr); validityPeriod.start kein Datum in der Zukunft; bei einer Teilabgabe verlängert sich die gesamte Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess).
 * **Privatrezept**: ab Erstelldatum maximal 365 Tage gültig, wenn die erste Einlösung innerhalb von 1 Monat ab Erstelldatum erfolgt (sonst Status abgelaufen). validityPeriod.start kein Datum in der Zukunft; Die Gültigkeitsdauer (validityPeriod.end) kann vom Arzt definiert werden.
@@ -1582,7 +1582,7 @@
 </t>
   </si>
   <si>
-    <t>Apotheke oder andere Einrichtung, die die geplante Abgabe einlösen soll. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Apotheke oder andere Einrichtung, die die Geplante Abgabe einlösen soll. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates the intended dispensing Organization specified by the prescriber.</t>
@@ -1594,7 +1594,7 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der die geplante Abgabe erstellt). Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der die Geplante Abgabe erstellt). Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -1674,7 +1674,7 @@
 </t>
   </si>
   <si>
-    <t>Im Falle einer Änderung wird auf die ersetzte geplante Abgabe verwiesen. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Im Falle einer Änderung wird auf die ersetzte Geplante Abgabe verwiesen. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>A link to a resource representing an earlier order related order or prescription.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:55+00:00</t>
+    <t>2026-06-22T09:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:33:42+00:00</t>
+    <t>2026-06-26T11:41:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:41:48+00:00</t>
+    <t>2026-06-30T14:26:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:26:32+00:00</t>
+    <t>2026-07-01T15:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:59:29+00:00</t>
+    <t>2026-07-06T05:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T05:37:07+00:00</t>
+    <t>2026-07-06T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:58:40+00:00</t>
+    <t>2026-07-06T16:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T16:22:02+00:00</t>
+    <t>2026-07-08T18:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T18:47:08+00:00</t>
+    <t>2026-07-08T22:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T22:06:32+00:00</t>
+    <t>2026-07-09T09:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:27:37+00:00</t>
+    <t>2026-07-09T10:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T10:22:28+00:00</t>
+    <t>2026-07-09T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T13:13:16+00:00</t>
+    <t>2026-07-09T17:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T17:30:16+00:00</t>
+    <t>2026-07-10T13:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T13:02:50+00:00</t>
+    <t>2026-07-13T07:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:52:05+00:00</t>
+    <t>2026-07-14T09:15:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:15:46+00:00</t>
+    <t>2026-07-17T15:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T15:29:52+00:00</t>
+    <t>2026-07-27T22:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T22:31:32+00:00</t>
+    <t>2026-07-28T00:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:05:30+00:00</t>
+    <t>2026-07-29T17:39:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:39:31+00:00</t>
+    <t>2026-08-26T12:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:55+00:00</t>
+    <t>2026-08-27T15:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:34:15+00:00</t>
+    <t>2026-08-31T18:38:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationRequest</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medicationrequest-base</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}allDosagesSameCategory:Alle Dosierungsanweisungen eines MedicationRequest müssen dieselbe Dosierungskategorie aufweisen. {dosageInstruction.extension.where(url = 'https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-dosage-category').value.coding.code.distinct().count() = 1}FirstDosageSequenceNumberExists:Wenn mehrere Dosierungsanweisungen vorhanden sind, muss mindestens eine davon die Sequenznummer 1 haben. {dosageInstruction.count() &lt;= 1 or dosageInstruction.sequence.where($this = 1).exists()}</t>
   </si>
   <si>
     <t>Request</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:38:38+00:00</t>
+    <t>2026-09-03T18:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-geplanteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T18:40:45+00:00</t>
+    <t>2026-09-10T13:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
